--- a/TestAirbyteSource.xlsx
+++ b/TestAirbyteSource.xlsx
@@ -1,20 +1,44 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Quantium-Dev\Downloads\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{54AE5773-37CB-4275-8F5B-BA38B8954896}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <bookViews>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+  </bookViews>
   <sheets>
-    <sheet state="visible" name="S.1" sheetId="1" r:id="rId5"/>
-    <sheet state="visible" name="Investran" sheetId="2" r:id="rId6"/>
+    <sheet name="S.1" sheetId="1" r:id="rId1"/>
+    <sheet name="Investran" sheetId="2" r:id="rId2"/>
+    <sheet name="Sheet1" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
     <definedName name="NamedRange1">S.1!$A$1:$N$2</definedName>
   </definedNames>
-  <calcPr/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="169" uniqueCount="73">
   <si>
     <t>Legal Entity</t>
   </si>
@@ -125,48 +149,192 @@
   </si>
   <si>
     <t>Cash Substitute</t>
+  </si>
+  <si>
+    <t>Entity:</t>
+  </si>
+  <si>
+    <t>Asset:</t>
+  </si>
+  <si>
+    <t>Currency:</t>
+  </si>
+  <si>
+    <t>Date:</t>
+  </si>
+  <si>
+    <t>Report:</t>
+  </si>
+  <si>
+    <t>Investor</t>
+  </si>
+  <si>
+    <t>LPID</t>
+  </si>
+  <si>
+    <t>Total Commitments</t>
+  </si>
+  <si>
+    <t>Unfunded investor commitment</t>
+  </si>
+  <si>
+    <t>Beginning Partners' Capital Account</t>
+  </si>
+  <si>
+    <t>Cumulative Capital Contributed since Inception</t>
+  </si>
+  <si>
+    <t>Equalisation Amounts due to LPs</t>
+  </si>
+  <si>
+    <t>Cumulative Net Capital Contributed since Inception (updated)</t>
+  </si>
+  <si>
+    <t>% Funded to date</t>
+  </si>
+  <si>
+    <t>Capital Distributions during the period</t>
+  </si>
+  <si>
+    <t>Dividend Income</t>
+  </si>
+  <si>
+    <t>Other Income</t>
+  </si>
+  <si>
+    <t>Interest Income (from Portfolio)</t>
+  </si>
+  <si>
+    <t>GP Remuneration</t>
+  </si>
+  <si>
+    <t>Investment Advisory Fees</t>
+  </si>
+  <si>
+    <t>Management Fees</t>
+  </si>
+  <si>
+    <t>Other Expenses</t>
+  </si>
+  <si>
+    <t>Net unrealised gain/(loss) on Investments</t>
+  </si>
+  <si>
+    <t>Net realized gain/(loss)</t>
+  </si>
+  <si>
+    <t>Cash FX translation gain/(loss)</t>
+  </si>
+  <si>
+    <t>Capital Account - before Carry</t>
+  </si>
+  <si>
+    <t>Carried Interest</t>
+  </si>
+  <si>
+    <t>Capital Account - after Carry</t>
+  </si>
+  <si>
+    <t>Net MoC - before Carry</t>
+  </si>
+  <si>
+    <t>#DIV/0!</t>
+  </si>
+  <si>
+    <t>Subtotal:Target Global Selected Opportunities, LLC - Series Actinium 1</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>Grand Total(s):</t>
+  </si>
+  <si>
+    <t>a</t>
+  </si>
+  <si>
+    <t>b</t>
+  </si>
+  <si>
+    <t>c</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="m/d/yyyy"/>
+    <numFmt numFmtId="164" formatCode="#,##0.00%"/>
   </numFmts>
-  <fonts count="5">
+  <fonts count="10">
     <font>
-      <sz val="10.0"/>
+      <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
     </font>
     <font>
+      <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="&quot;Aptos Narrow&quot;"/>
     </font>
     <font>
       <b/>
-      <sz val="11.0"/>
+      <sz val="11"/>
       <color rgb="FFFFFFFF"/>
       <name val="Calibri"/>
     </font>
     <font>
+      <sz val="10"/>
       <color theme="1"/>
       <name val="Arial"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Avenir Book"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Avenir Next Regular"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="5">
+  <fills count="10">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
-      <patternFill patternType="lightGray"/>
+      <patternFill patternType="gray125"/>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -186,9 +354,41 @@
         <bgColor rgb="FFA5A5A5"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFECECEC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD1DDED"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF657A98"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="6">
-    <border/>
+  <borders count="13">
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
     <border>
       <left style="thin">
         <color rgb="FF000000"/>
@@ -202,8 +402,10 @@
       <bottom style="thin">
         <color rgb="FF000000"/>
       </bottom>
+      <diagonal/>
     </border>
     <border>
+      <left/>
       <right style="thin">
         <color rgb="FF000000"/>
       </right>
@@ -213,27 +415,34 @@
       <bottom style="thin">
         <color rgb="FF000000"/>
       </bottom>
+      <diagonal/>
     </border>
     <border>
       <left style="thin">
         <color rgb="FFC9C9C9"/>
       </left>
+      <right/>
       <top style="thin">
         <color rgb="FFC9C9C9"/>
       </top>
       <bottom style="thin">
         <color rgb="FFC9C9C9"/>
       </bottom>
+      <diagonal/>
     </border>
     <border>
+      <left/>
+      <right/>
       <top style="thin">
         <color rgb="FFC9C9C9"/>
       </top>
       <bottom style="thin">
         <color rgb="FFC9C9C9"/>
       </bottom>
+      <diagonal/>
     </border>
     <border>
+      <left/>
       <right style="thin">
         <color rgb="FFC9C9C9"/>
       </right>
@@ -243,86 +452,235 @@
       <bottom style="thin">
         <color rgb="FFC9C9C9"/>
       </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thick">
+        <color auto="1"/>
+      </left>
+      <right style="thick">
+        <color auto="1"/>
+      </right>
+      <top style="thick">
+        <color auto="1"/>
+      </top>
+      <bottom style="thick">
+        <color auto="1"/>
+      </bottom>
+      <diagonal style="thick">
+        <color auto="1"/>
+      </diagonal>
+    </border>
+    <border>
+      <left style="thick">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal style="thin">
+        <color auto="1"/>
+      </diagonal>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal style="thin">
+        <color auto="1"/>
+      </diagonal>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thick">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal style="thin">
+        <color auto="1"/>
+      </diagonal>
+    </border>
+    <border>
+      <left style="thick">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thick">
+        <color auto="1"/>
+      </bottom>
+      <diagonal style="thin">
+        <color auto="1"/>
+      </diagonal>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thick">
+        <color auto="1"/>
+      </bottom>
+      <diagonal style="thin">
+        <color auto="1"/>
+      </diagonal>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thick">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thick">
+        <color auto="1"/>
+      </bottom>
+      <diagonal style="thin">
+        <color auto="1"/>
+      </diagonal>
     </border>
   </borders>
-  <cellStyleXfs count="1">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
+  <cellStyleXfs count="4">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+  <cellXfs count="38">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf borderId="1" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf borderId="1" fillId="2" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
     </xf>
-    <xf borderId="1" fillId="3" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment readingOrder="0"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="14" fontId="2" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
     </xf>
-    <xf borderId="1" fillId="3" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="right" readingOrder="0"/>
+    <xf numFmtId="4" fontId="2" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
     </xf>
-    <xf borderId="1" fillId="3" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment readingOrder="0"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
     </xf>
-    <xf borderId="1" fillId="3" fontId="2" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="right" readingOrder="0" shrinkToFit="0" wrapText="0"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="14" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="4" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top"/>
     </xf>
-    <xf borderId="1" fillId="3" fontId="2" numFmtId="4" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="right" readingOrder="0" shrinkToFit="0" wrapText="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="0" xfId="2" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="3"/>
+    <xf numFmtId="14" fontId="6" fillId="5" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
-    <xf borderId="1" fillId="3" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="right" readingOrder="0" shrinkToFit="0" wrapText="0"/>
+    <xf numFmtId="14" fontId="8" fillId="5" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
-    <xf borderId="1" fillId="3" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="right" readingOrder="0"/>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="6" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="2" fillId="3" fontId="2" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="3" fillId="4" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment readingOrder="0"/>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="8" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
-    <xf borderId="4" fillId="4" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment readingOrder="0"/>
+    <xf numFmtId="4" fontId="5" fillId="7" borderId="8" xfId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf borderId="5" fillId="4" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment readingOrder="0"/>
+    <xf numFmtId="164" fontId="5" fillId="7" borderId="8" xfId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0"/>
+    <xf numFmtId="4" fontId="5" fillId="7" borderId="9" xfId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="4" numFmtId="164" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
-      <alignment readingOrder="0"/>
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="7" xfId="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="8" xfId="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="4" fontId="9" fillId="8" borderId="8" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="4" numFmtId="4" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
-      <alignment readingOrder="0"/>
+    <xf numFmtId="164" fontId="9" fillId="8" borderId="8" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" vertical="top"/>
+    <xf numFmtId="4" fontId="9" fillId="8" borderId="9" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="9" borderId="10" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="9" borderId="11" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="4" fontId="9" fillId="9" borderId="11" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="9" borderId="11" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="9" fillId="9" borderId="12" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
     </xf>
   </cellXfs>
-  <cellStyles count="1">
-    <cellStyle xfId="0" name="Normal" builtinId="0"/>
+  <cellStyles count="4">
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal 2" xfId="1" xr:uid="{85D86440-C5D9-4E06-B608-FE7F9CBDFCB0}"/>
+    <cellStyle name="Normal 3" xfId="3" xr:uid="{A36E421F-A509-4B92-AD5C-2D1D6EA2D12B}"/>
+    <cellStyle name="Normal 4" xfId="2" xr:uid="{A26D1F85-82D7-46EE-A919-650A9EA1FAD0}"/>
   </cellStyles>
   <dxfs count="0"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
-<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
-</file>
-
-<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<x18tc:personList xmlns:x18tc="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments"/>
-</file>
-
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheets">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Sheets">
   <a:themeElements>
     <a:clrScheme name="Sheets">
       <a:dk1>
@@ -512,20 +870,23 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
+  <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <dimension ref="A1:N2"/>
+  <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
-    <col customWidth="1" min="13" max="13" width="38.25"/>
+    <col min="13" max="13" width="38.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:14">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -569,18 +930,18 @@
         <v>13</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" spans="1:14">
       <c r="A2" s="3" t="s">
         <v>0</v>
       </c>
       <c r="B2" s="4">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="C2" s="5" t="s">
         <v>14</v>
       </c>
       <c r="D2" s="6">
-        <v>44214.0</v>
+        <v>44214</v>
       </c>
       <c r="E2" s="5" t="s">
         <v>15</v>
@@ -595,154 +956,164 @@
         <v>18</v>
       </c>
       <c r="I2" s="7">
-        <v>200000.0</v>
+        <v>200000</v>
       </c>
       <c r="J2" s="8">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="K2" s="7">
-        <v>200000.0</v>
-      </c>
-      <c r="L2" s="9">
-        <v>9081.0</v>
+        <v>200000</v>
+      </c>
+      <c r="L2" s="8">
+        <v>9081</v>
       </c>
       <c r="M2" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="N2" s="10"/>
+      <c r="N2" s="9"/>
     </row>
   </sheetData>
-  <drawing r:id="rId1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <dimension ref="A1:P14"/>
+  <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
-    <col customWidth="1" min="1" max="1" width="20.13"/>
-    <col customWidth="1" min="2" max="2" width="19.13"/>
-    <col customWidth="1" min="3" max="3" width="16.13"/>
-    <col customWidth="1" min="4" max="4" width="13.38"/>
-    <col customWidth="1" min="5" max="5" width="7.38"/>
-    <col customWidth="1" min="6" max="6" width="10.38"/>
-    <col customWidth="1" min="7" max="7" width="17.63"/>
-    <col customWidth="1" min="8" max="8" width="13.38"/>
-    <col customWidth="1" min="9" max="9" width="32.63"/>
-    <col customWidth="1" min="10" max="10" width="31.5"/>
-    <col customWidth="1" min="11" max="11" width="11.5"/>
-    <col customWidth="1" min="12" max="12" width="16.38"/>
-    <col customWidth="1" min="13" max="13" width="15.0"/>
-    <col customWidth="1" min="14" max="14" width="38.75"/>
-    <col customWidth="1" min="15" max="15" width="30.25"/>
-    <col customWidth="1" min="16" max="16" width="12.75"/>
+    <col min="1" max="1" width="20.140625" customWidth="1"/>
+    <col min="2" max="2" width="19.140625" customWidth="1"/>
+    <col min="3" max="3" width="16.140625" customWidth="1"/>
+    <col min="4" max="4" width="13.42578125" customWidth="1"/>
+    <col min="5" max="5" width="7.42578125" customWidth="1"/>
+    <col min="6" max="6" width="10.42578125" customWidth="1"/>
+    <col min="7" max="7" width="17.5703125" customWidth="1"/>
+    <col min="8" max="8" width="13.42578125" customWidth="1"/>
+    <col min="9" max="9" width="32.5703125" customWidth="1"/>
+    <col min="10" max="10" width="31.42578125" customWidth="1"/>
+    <col min="11" max="11" width="11.42578125" customWidth="1"/>
+    <col min="12" max="12" width="16.42578125" customWidth="1"/>
+    <col min="13" max="13" width="15" customWidth="1"/>
+    <col min="14" max="14" width="38.7109375" customWidth="1"/>
+    <col min="15" max="15" width="30.28515625" customWidth="1"/>
+    <col min="16" max="16" width="12.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="11" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="12" t="s">
+    <row r="1" spans="1:16" ht="15.75" customHeight="1">
+      <c r="A1" s="10" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="11" t="s">
         <v>20</v>
       </c>
-      <c r="C1" s="12" t="s">
+      <c r="C1" s="11" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="12" t="s">
+      <c r="D1" s="11" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="12" t="s">
+      <c r="E1" s="11" t="s">
         <v>11</v>
       </c>
-      <c r="F1" s="12" t="s">
+      <c r="F1" s="11" t="s">
         <v>4</v>
       </c>
-      <c r="G1" s="12" t="s">
+      <c r="G1" s="11" t="s">
         <v>7</v>
       </c>
-      <c r="H1" s="12" t="s">
+      <c r="H1" s="11" t="s">
         <v>5</v>
       </c>
-      <c r="I1" s="12" t="s">
+      <c r="I1" s="11" t="s">
         <v>6</v>
       </c>
-      <c r="J1" s="12" t="s">
+      <c r="J1" s="11" t="s">
         <v>21</v>
       </c>
-      <c r="K1" s="12" t="s">
+      <c r="K1" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="L1" s="12" t="s">
+      <c r="L1" s="11" t="s">
         <v>23</v>
       </c>
-      <c r="M1" s="12" t="s">
+      <c r="M1" s="11" t="s">
         <v>24</v>
       </c>
-      <c r="N1" s="12" t="s">
+      <c r="N1" s="11" t="s">
         <v>12</v>
       </c>
-      <c r="O1" s="12" t="s">
+      <c r="O1" s="11" t="s">
         <v>25</v>
       </c>
-      <c r="P1" s="13" t="s">
+      <c r="P1" s="12" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" s="14" t="s">
+    <row r="2" spans="1:16">
+      <c r="A2" s="13" t="s">
         <v>27</v>
       </c>
-      <c r="B2" s="14" t="s">
+      <c r="B2" s="13" t="s">
         <v>28</v>
       </c>
-      <c r="C2" s="14" t="s">
+      <c r="C2" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="D2" s="15">
-        <v>44980.0</v>
-      </c>
-      <c r="E2" s="14">
-        <v>40404.0</v>
-      </c>
-      <c r="F2" s="14" t="s">
+      <c r="D2" s="14">
+        <v>44980</v>
+      </c>
+      <c r="E2" s="13">
+        <v>40404</v>
+      </c>
+      <c r="F2" s="13" t="s">
         <v>15</v>
       </c>
-      <c r="G2" s="14" t="s">
+      <c r="G2" s="13" t="s">
         <v>30</v>
       </c>
-      <c r="H2" s="14" t="s">
+      <c r="H2" s="13" t="s">
         <v>31</v>
       </c>
-      <c r="I2" s="14" t="s">
+      <c r="I2" s="13" t="s">
         <v>32</v>
       </c>
-      <c r="J2" s="14" t="s">
+      <c r="J2" s="13" t="s">
         <v>33</v>
       </c>
-      <c r="K2" s="16">
-        <v>57545.0</v>
-      </c>
-      <c r="L2" s="16">
-        <v>57545.0</v>
-      </c>
-      <c r="M2" s="14">
-        <v>1.0</v>
-      </c>
-      <c r="N2" s="14" t="s">
+      <c r="K2" s="15">
+        <v>57545</v>
+      </c>
+      <c r="L2" s="15">
+        <v>57545</v>
+      </c>
+      <c r="M2" s="13">
+        <v>1</v>
+      </c>
+      <c r="N2" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="O2" s="14" t="s">
+      <c r="O2" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="P2" s="14" t="s">
+      <c r="P2" s="13" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="6">
-      <c r="K6" s="17"/>
+    <row r="6" spans="1:16">
+      <c r="K6" s="16"/>
+      <c r="L6" s="17"/>
+      <c r="N6" s="17"/>
+      <c r="O6" s="17"/>
+    </row>
+    <row r="14" spans="1:16" ht="15.75" customHeight="1">
+      <c r="K14" s="17"/>
+      <c r="L14" s="17"/>
+      <c r="N14" s="17"/>
+      <c r="O14" s="17"/>
     </row>
   </sheetData>
   <mergeCells count="4">
@@ -751,6 +1122,1793 @@
     <mergeCell ref="K14:L14"/>
     <mergeCell ref="N14:O14"/>
   </mergeCells>
-  <drawing r:id="rId1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C0853327-519A-48CE-A554-A78DA76CA024}">
+  <dimension ref="A1:Z27"/>
+  <sheetFormatPr defaultRowHeight="12.75"/>
+  <sheetData>
+    <row r="1" spans="1:26">
+      <c r="A1" s="18" t="s">
+        <v>37</v>
+      </c>
+      <c r="B1" s="19">
+        <v>1</v>
+      </c>
+      <c r="C1" s="20"/>
+      <c r="D1" s="20"/>
+      <c r="E1" s="20"/>
+      <c r="F1" s="20"/>
+      <c r="G1" s="20"/>
+      <c r="H1" s="20"/>
+      <c r="I1" s="20"/>
+      <c r="J1" s="20"/>
+      <c r="K1" s="20"/>
+      <c r="L1" s="20"/>
+      <c r="M1" s="20"/>
+      <c r="N1" s="20"/>
+      <c r="O1" s="20"/>
+      <c r="P1" s="20"/>
+      <c r="Q1" s="20"/>
+      <c r="R1" s="20"/>
+      <c r="S1" s="20"/>
+      <c r="T1" s="20"/>
+      <c r="U1" s="20"/>
+      <c r="V1" s="20"/>
+      <c r="W1" s="20"/>
+      <c r="X1" s="20"/>
+      <c r="Y1" s="20"/>
+      <c r="Z1" s="20"/>
+    </row>
+    <row r="2" spans="1:26">
+      <c r="A2" s="18" t="s">
+        <v>38</v>
+      </c>
+      <c r="B2" s="19">
+        <v>1</v>
+      </c>
+      <c r="C2" s="20"/>
+      <c r="D2" s="20"/>
+      <c r="E2" s="20"/>
+      <c r="F2" s="20"/>
+      <c r="G2" s="20"/>
+      <c r="H2" s="20"/>
+      <c r="I2" s="20"/>
+      <c r="J2" s="20"/>
+      <c r="K2" s="20"/>
+      <c r="L2" s="20"/>
+      <c r="M2" s="20"/>
+      <c r="N2" s="20"/>
+      <c r="O2" s="20"/>
+      <c r="P2" s="20"/>
+      <c r="Q2" s="20"/>
+      <c r="R2" s="20"/>
+      <c r="S2" s="20"/>
+      <c r="T2" s="20"/>
+      <c r="U2" s="20"/>
+      <c r="V2" s="20"/>
+      <c r="W2" s="20"/>
+      <c r="X2" s="20"/>
+      <c r="Y2" s="20"/>
+      <c r="Z2" s="20"/>
+    </row>
+    <row r="3" spans="1:26">
+      <c r="A3" s="18" t="s">
+        <v>39</v>
+      </c>
+      <c r="B3" s="19">
+        <v>1</v>
+      </c>
+      <c r="C3" s="20"/>
+      <c r="D3" s="20"/>
+      <c r="E3" s="20"/>
+      <c r="F3" s="20"/>
+      <c r="G3" s="20"/>
+      <c r="H3" s="20"/>
+      <c r="I3" s="20"/>
+      <c r="J3" s="20"/>
+      <c r="K3" s="20"/>
+      <c r="L3" s="20"/>
+      <c r="M3" s="20"/>
+      <c r="N3" s="20"/>
+      <c r="O3" s="20"/>
+      <c r="P3" s="20"/>
+      <c r="Q3" s="20"/>
+      <c r="R3" s="20"/>
+      <c r="S3" s="20"/>
+      <c r="T3" s="20"/>
+      <c r="U3" s="20"/>
+      <c r="V3" s="20"/>
+      <c r="W3" s="20"/>
+      <c r="X3" s="20"/>
+      <c r="Y3" s="20"/>
+      <c r="Z3" s="20"/>
+    </row>
+    <row r="4" spans="1:26">
+      <c r="A4" s="18" t="s">
+        <v>40</v>
+      </c>
+      <c r="B4" s="21">
+        <v>1</v>
+      </c>
+      <c r="C4" s="20"/>
+      <c r="D4" s="20"/>
+      <c r="E4" s="20"/>
+      <c r="F4" s="20"/>
+      <c r="G4" s="20"/>
+      <c r="H4" s="20"/>
+      <c r="I4" s="20"/>
+      <c r="J4" s="20"/>
+      <c r="K4" s="20"/>
+      <c r="L4" s="20"/>
+      <c r="M4" s="20"/>
+      <c r="N4" s="20"/>
+      <c r="O4" s="20"/>
+      <c r="P4" s="20"/>
+      <c r="Q4" s="20"/>
+      <c r="R4" s="20"/>
+      <c r="S4" s="20"/>
+      <c r="T4" s="20"/>
+      <c r="U4" s="20"/>
+      <c r="V4" s="20"/>
+      <c r="W4" s="20"/>
+      <c r="X4" s="20"/>
+      <c r="Y4" s="20"/>
+      <c r="Z4" s="20"/>
+    </row>
+    <row r="5" spans="1:26">
+      <c r="A5" s="18" t="s">
+        <v>41</v>
+      </c>
+      <c r="B5" s="22">
+        <v>123123213213</v>
+      </c>
+      <c r="C5" s="20"/>
+      <c r="D5" s="20"/>
+      <c r="E5" s="20"/>
+      <c r="F5" s="20"/>
+      <c r="G5" s="20"/>
+      <c r="H5" s="20"/>
+      <c r="I5" s="20"/>
+      <c r="J5" s="20"/>
+      <c r="K5" s="20"/>
+      <c r="L5" s="20"/>
+      <c r="M5" s="20"/>
+      <c r="N5" s="20"/>
+      <c r="O5" s="20"/>
+      <c r="P5" s="20"/>
+      <c r="Q5" s="20"/>
+      <c r="R5" s="20"/>
+      <c r="S5" s="20"/>
+      <c r="T5" s="20"/>
+      <c r="U5" s="20"/>
+      <c r="V5" s="20"/>
+      <c r="W5" s="20"/>
+      <c r="X5" s="20"/>
+      <c r="Y5" s="20"/>
+      <c r="Z5" s="20"/>
+    </row>
+    <row r="6" spans="1:26">
+      <c r="A6" s="20"/>
+      <c r="B6" s="20"/>
+      <c r="C6" s="20"/>
+      <c r="D6" s="20"/>
+      <c r="E6" s="20"/>
+      <c r="F6" s="20"/>
+      <c r="G6" s="20"/>
+      <c r="H6" s="20"/>
+      <c r="I6" s="20"/>
+      <c r="J6" s="20"/>
+      <c r="K6" s="20"/>
+      <c r="L6" s="20"/>
+      <c r="M6" s="20"/>
+      <c r="N6" s="20"/>
+      <c r="O6" s="20"/>
+      <c r="P6" s="20"/>
+      <c r="Q6" s="20"/>
+      <c r="R6" s="20"/>
+      <c r="S6" s="20"/>
+      <c r="T6" s="20"/>
+      <c r="U6" s="20"/>
+      <c r="V6" s="20"/>
+      <c r="W6" s="20"/>
+      <c r="X6" s="20"/>
+      <c r="Y6" s="20"/>
+      <c r="Z6" s="20"/>
+    </row>
+    <row r="7" spans="1:26" ht="13.5" thickBot="1">
+      <c r="A7" s="20"/>
+      <c r="B7" s="20"/>
+      <c r="C7" s="20">
+        <v>1</v>
+      </c>
+      <c r="D7" s="20">
+        <v>2</v>
+      </c>
+      <c r="E7" s="20">
+        <v>3</v>
+      </c>
+      <c r="F7" s="20">
+        <v>4</v>
+      </c>
+      <c r="G7" s="20">
+        <v>5</v>
+      </c>
+      <c r="H7" s="20">
+        <v>6</v>
+      </c>
+      <c r="I7" s="20">
+        <v>7</v>
+      </c>
+      <c r="J7" s="20">
+        <v>8</v>
+      </c>
+      <c r="K7" s="20">
+        <v>9</v>
+      </c>
+      <c r="L7" s="20">
+        <v>10</v>
+      </c>
+      <c r="M7" s="20">
+        <v>11</v>
+      </c>
+      <c r="N7" s="20">
+        <v>12</v>
+      </c>
+      <c r="O7" s="20">
+        <v>13</v>
+      </c>
+      <c r="P7" s="20">
+        <v>14</v>
+      </c>
+      <c r="Q7" s="20">
+        <v>15</v>
+      </c>
+      <c r="R7" s="20">
+        <v>16</v>
+      </c>
+      <c r="S7" s="20">
+        <v>17</v>
+      </c>
+      <c r="T7" s="20">
+        <v>18</v>
+      </c>
+      <c r="U7" s="20">
+        <v>19</v>
+      </c>
+      <c r="V7" s="20">
+        <v>20</v>
+      </c>
+      <c r="W7" s="20"/>
+      <c r="X7" s="20"/>
+      <c r="Y7" s="20"/>
+      <c r="Z7" s="20"/>
+    </row>
+    <row r="8" spans="1:26" ht="151.5" thickTop="1" thickBot="1">
+      <c r="A8" s="23" t="s">
+        <v>0</v>
+      </c>
+      <c r="B8" s="23" t="s">
+        <v>20</v>
+      </c>
+      <c r="C8" s="23" t="s">
+        <v>42</v>
+      </c>
+      <c r="D8" s="23" t="s">
+        <v>43</v>
+      </c>
+      <c r="E8" s="23" t="s">
+        <v>44</v>
+      </c>
+      <c r="F8" s="23" t="s">
+        <v>45</v>
+      </c>
+      <c r="G8" s="23" t="s">
+        <v>46</v>
+      </c>
+      <c r="H8" s="23" t="s">
+        <v>47</v>
+      </c>
+      <c r="I8" s="23" t="s">
+        <v>48</v>
+      </c>
+      <c r="J8" s="23" t="s">
+        <v>49</v>
+      </c>
+      <c r="K8" s="23" t="s">
+        <v>50</v>
+      </c>
+      <c r="L8" s="23" t="s">
+        <v>51</v>
+      </c>
+      <c r="M8" s="23" t="s">
+        <v>52</v>
+      </c>
+      <c r="N8" s="23" t="s">
+        <v>53</v>
+      </c>
+      <c r="O8" s="23" t="s">
+        <v>54</v>
+      </c>
+      <c r="P8" s="23" t="s">
+        <v>55</v>
+      </c>
+      <c r="Q8" s="23" t="s">
+        <v>56</v>
+      </c>
+      <c r="R8" s="23" t="s">
+        <v>57</v>
+      </c>
+      <c r="S8" s="23" t="s">
+        <v>58</v>
+      </c>
+      <c r="T8" s="23" t="s">
+        <v>59</v>
+      </c>
+      <c r="U8" s="23" t="s">
+        <v>60</v>
+      </c>
+      <c r="V8" s="23" t="s">
+        <v>61</v>
+      </c>
+      <c r="W8" s="23" t="s">
+        <v>62</v>
+      </c>
+      <c r="X8" s="23" t="s">
+        <v>63</v>
+      </c>
+      <c r="Y8" s="23" t="s">
+        <v>64</v>
+      </c>
+      <c r="Z8" s="23" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="9" spans="1:26" ht="15.75" thickTop="1">
+      <c r="A9" s="24" t="s">
+        <v>70</v>
+      </c>
+      <c r="B9" s="24" t="s">
+        <v>70</v>
+      </c>
+      <c r="C9" s="24" t="s">
+        <v>70</v>
+      </c>
+      <c r="D9" s="24" t="s">
+        <v>70</v>
+      </c>
+      <c r="E9" s="25">
+        <v>0</v>
+      </c>
+      <c r="F9" s="25">
+        <v>0</v>
+      </c>
+      <c r="G9" s="25">
+        <v>0</v>
+      </c>
+      <c r="H9" s="25">
+        <v>0</v>
+      </c>
+      <c r="I9" s="25">
+        <v>0</v>
+      </c>
+      <c r="J9" s="25">
+        <v>0</v>
+      </c>
+      <c r="K9" s="26" t="s">
+        <v>66</v>
+      </c>
+      <c r="L9" s="25">
+        <v>0</v>
+      </c>
+      <c r="M9" s="25">
+        <v>0</v>
+      </c>
+      <c r="N9" s="25">
+        <v>0</v>
+      </c>
+      <c r="O9" s="25">
+        <v>0</v>
+      </c>
+      <c r="P9" s="25">
+        <v>0</v>
+      </c>
+      <c r="Q9" s="25">
+        <v>0</v>
+      </c>
+      <c r="R9" s="25">
+        <v>0</v>
+      </c>
+      <c r="S9" s="25">
+        <v>0</v>
+      </c>
+      <c r="T9" s="25">
+        <v>0</v>
+      </c>
+      <c r="U9" s="25">
+        <v>0</v>
+      </c>
+      <c r="V9" s="25">
+        <v>0</v>
+      </c>
+      <c r="W9" s="25">
+        <v>0</v>
+      </c>
+      <c r="X9" s="25">
+        <v>0</v>
+      </c>
+      <c r="Y9" s="25">
+        <v>0</v>
+      </c>
+      <c r="Z9" s="27" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="10" spans="1:26" ht="15">
+      <c r="A10" s="24" t="s">
+        <v>71</v>
+      </c>
+      <c r="B10" s="24" t="s">
+        <v>71</v>
+      </c>
+      <c r="C10" s="24" t="s">
+        <v>71</v>
+      </c>
+      <c r="D10" s="24" t="s">
+        <v>71</v>
+      </c>
+      <c r="E10" s="25">
+        <v>199104.88</v>
+      </c>
+      <c r="F10" s="25">
+        <v>0</v>
+      </c>
+      <c r="G10" s="25">
+        <v>0</v>
+      </c>
+      <c r="H10" s="25">
+        <v>199104.88</v>
+      </c>
+      <c r="I10" s="25">
+        <v>0</v>
+      </c>
+      <c r="J10" s="25">
+        <v>199104.88</v>
+      </c>
+      <c r="K10" s="26">
+        <v>1</v>
+      </c>
+      <c r="L10" s="25">
+        <v>0</v>
+      </c>
+      <c r="M10" s="25">
+        <v>0</v>
+      </c>
+      <c r="N10" s="25">
+        <v>0</v>
+      </c>
+      <c r="O10" s="25">
+        <v>0</v>
+      </c>
+      <c r="P10" s="25">
+        <v>0</v>
+      </c>
+      <c r="Q10" s="25">
+        <v>0</v>
+      </c>
+      <c r="R10" s="25">
+        <v>0</v>
+      </c>
+      <c r="S10" s="25">
+        <v>-1727.49</v>
+      </c>
+      <c r="T10" s="25">
+        <v>568485.76</v>
+      </c>
+      <c r="U10" s="25">
+        <v>0</v>
+      </c>
+      <c r="V10" s="25">
+        <v>0</v>
+      </c>
+      <c r="W10" s="25">
+        <v>765863.15</v>
+      </c>
+      <c r="X10" s="25">
+        <v>-55784.63</v>
+      </c>
+      <c r="Y10" s="25">
+        <v>710078.52</v>
+      </c>
+      <c r="Z10" s="27">
+        <v>3.85</v>
+      </c>
+    </row>
+    <row r="11" spans="1:26" ht="15">
+      <c r="A11" s="24" t="s">
+        <v>72</v>
+      </c>
+      <c r="B11" s="24" t="s">
+        <v>72</v>
+      </c>
+      <c r="C11" s="24" t="s">
+        <v>72</v>
+      </c>
+      <c r="D11" s="24" t="s">
+        <v>72</v>
+      </c>
+      <c r="E11" s="25">
+        <v>284801.36</v>
+      </c>
+      <c r="F11" s="25">
+        <v>0</v>
+      </c>
+      <c r="G11" s="25">
+        <v>0</v>
+      </c>
+      <c r="H11" s="25">
+        <v>284801.36</v>
+      </c>
+      <c r="I11" s="25">
+        <v>0</v>
+      </c>
+      <c r="J11" s="25">
+        <v>284801.36</v>
+      </c>
+      <c r="K11" s="26">
+        <v>1</v>
+      </c>
+      <c r="L11" s="25">
+        <v>0</v>
+      </c>
+      <c r="M11" s="25">
+        <v>0</v>
+      </c>
+      <c r="N11" s="25">
+        <v>0</v>
+      </c>
+      <c r="O11" s="25">
+        <v>0</v>
+      </c>
+      <c r="P11" s="25">
+        <v>0</v>
+      </c>
+      <c r="Q11" s="25">
+        <v>0</v>
+      </c>
+      <c r="R11" s="25">
+        <v>0</v>
+      </c>
+      <c r="S11" s="25">
+        <v>-2471</v>
+      </c>
+      <c r="T11" s="25">
+        <v>813209.22</v>
+      </c>
+      <c r="U11" s="25">
+        <v>0</v>
+      </c>
+      <c r="V11" s="25">
+        <v>0</v>
+      </c>
+      <c r="W11" s="25">
+        <v>1095539.58</v>
+      </c>
+      <c r="X11" s="25">
+        <v>-154134.57999999999</v>
+      </c>
+      <c r="Y11" s="25">
+        <v>941405</v>
+      </c>
+      <c r="Z11" s="27">
+        <v>3.85</v>
+      </c>
+    </row>
+    <row r="12" spans="1:26" ht="15">
+      <c r="A12" s="24" t="s">
+        <v>70</v>
+      </c>
+      <c r="B12" s="24" t="s">
+        <v>70</v>
+      </c>
+      <c r="C12" s="24" t="s">
+        <v>70</v>
+      </c>
+      <c r="D12" s="24" t="s">
+        <v>70</v>
+      </c>
+      <c r="E12" s="25">
+        <v>391832.08</v>
+      </c>
+      <c r="F12" s="25">
+        <v>0</v>
+      </c>
+      <c r="G12" s="25">
+        <v>0</v>
+      </c>
+      <c r="H12" s="25">
+        <v>391832.08</v>
+      </c>
+      <c r="I12" s="25">
+        <v>0</v>
+      </c>
+      <c r="J12" s="25">
+        <v>391832.08</v>
+      </c>
+      <c r="K12" s="26">
+        <v>1</v>
+      </c>
+      <c r="L12" s="25">
+        <v>0</v>
+      </c>
+      <c r="M12" s="25">
+        <v>0</v>
+      </c>
+      <c r="N12" s="25">
+        <v>0</v>
+      </c>
+      <c r="O12" s="25">
+        <v>0</v>
+      </c>
+      <c r="P12" s="25">
+        <v>0</v>
+      </c>
+      <c r="Q12" s="25">
+        <v>0</v>
+      </c>
+      <c r="R12" s="25">
+        <v>0</v>
+      </c>
+      <c r="S12" s="25">
+        <v>-3399.62</v>
+      </c>
+      <c r="T12" s="25">
+        <v>1118805.95</v>
+      </c>
+      <c r="U12" s="25">
+        <v>0</v>
+      </c>
+      <c r="V12" s="25">
+        <v>0</v>
+      </c>
+      <c r="W12" s="25">
+        <v>1507238.41</v>
+      </c>
+      <c r="X12" s="25">
+        <v>-216593.59</v>
+      </c>
+      <c r="Y12" s="25">
+        <v>1290644.82</v>
+      </c>
+      <c r="Z12" s="27">
+        <v>3.85</v>
+      </c>
+    </row>
+    <row r="13" spans="1:26" ht="15">
+      <c r="A13" s="24" t="s">
+        <v>71</v>
+      </c>
+      <c r="B13" s="24" t="s">
+        <v>71</v>
+      </c>
+      <c r="C13" s="24" t="s">
+        <v>71</v>
+      </c>
+      <c r="D13" s="24" t="s">
+        <v>71</v>
+      </c>
+      <c r="E13" s="25">
+        <v>0</v>
+      </c>
+      <c r="F13" s="25">
+        <v>0</v>
+      </c>
+      <c r="G13" s="25">
+        <v>0</v>
+      </c>
+      <c r="H13" s="25">
+        <v>0</v>
+      </c>
+      <c r="I13" s="25">
+        <v>0</v>
+      </c>
+      <c r="J13" s="25">
+        <v>0</v>
+      </c>
+      <c r="K13" s="26" t="s">
+        <v>66</v>
+      </c>
+      <c r="L13" s="25">
+        <v>0</v>
+      </c>
+      <c r="M13" s="25">
+        <v>0</v>
+      </c>
+      <c r="N13" s="25">
+        <v>0</v>
+      </c>
+      <c r="O13" s="25">
+        <v>0</v>
+      </c>
+      <c r="P13" s="25">
+        <v>0</v>
+      </c>
+      <c r="Q13" s="25">
+        <v>0</v>
+      </c>
+      <c r="R13" s="25">
+        <v>0</v>
+      </c>
+      <c r="S13" s="25">
+        <v>0</v>
+      </c>
+      <c r="T13" s="25">
+        <v>0</v>
+      </c>
+      <c r="U13" s="25">
+        <v>0</v>
+      </c>
+      <c r="V13" s="25">
+        <v>0</v>
+      </c>
+      <c r="W13" s="25">
+        <v>0</v>
+      </c>
+      <c r="X13" s="25">
+        <v>0</v>
+      </c>
+      <c r="Y13" s="25">
+        <v>0</v>
+      </c>
+      <c r="Z13" s="27" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="14" spans="1:26" ht="15">
+      <c r="A14" s="24" t="s">
+        <v>72</v>
+      </c>
+      <c r="B14" s="24" t="s">
+        <v>72</v>
+      </c>
+      <c r="C14" s="24" t="s">
+        <v>72</v>
+      </c>
+      <c r="D14" s="24" t="s">
+        <v>72</v>
+      </c>
+      <c r="E14" s="25">
+        <v>250143.92</v>
+      </c>
+      <c r="F14" s="25">
+        <v>0</v>
+      </c>
+      <c r="G14" s="25">
+        <v>0</v>
+      </c>
+      <c r="H14" s="25">
+        <v>250143.92</v>
+      </c>
+      <c r="I14" s="25">
+        <v>0</v>
+      </c>
+      <c r="J14" s="25">
+        <v>250143.92</v>
+      </c>
+      <c r="K14" s="26">
+        <v>1</v>
+      </c>
+      <c r="L14" s="25">
+        <v>0</v>
+      </c>
+      <c r="M14" s="25">
+        <v>0</v>
+      </c>
+      <c r="N14" s="25">
+        <v>0</v>
+      </c>
+      <c r="O14" s="25">
+        <v>0</v>
+      </c>
+      <c r="P14" s="25">
+        <v>0</v>
+      </c>
+      <c r="Q14" s="25">
+        <v>0</v>
+      </c>
+      <c r="R14" s="25">
+        <v>0</v>
+      </c>
+      <c r="S14" s="25">
+        <v>-2170.31</v>
+      </c>
+      <c r="T14" s="25">
+        <v>714226.58</v>
+      </c>
+      <c r="U14" s="25">
+        <v>0</v>
+      </c>
+      <c r="V14" s="25">
+        <v>0</v>
+      </c>
+      <c r="W14" s="25">
+        <v>962200.19</v>
+      </c>
+      <c r="X14" s="25">
+        <v>-136340.14000000001</v>
+      </c>
+      <c r="Y14" s="25">
+        <v>825860.05</v>
+      </c>
+      <c r="Z14" s="27">
+        <v>3.85</v>
+      </c>
+    </row>
+    <row r="15" spans="1:26" ht="15">
+      <c r="A15" s="24" t="s">
+        <v>70</v>
+      </c>
+      <c r="B15" s="24" t="s">
+        <v>70</v>
+      </c>
+      <c r="C15" s="24" t="s">
+        <v>70</v>
+      </c>
+      <c r="D15" s="24" t="s">
+        <v>70</v>
+      </c>
+      <c r="E15" s="25">
+        <v>0</v>
+      </c>
+      <c r="F15" s="25">
+        <v>0</v>
+      </c>
+      <c r="G15" s="25">
+        <v>0</v>
+      </c>
+      <c r="H15" s="25">
+        <v>0</v>
+      </c>
+      <c r="I15" s="25">
+        <v>0</v>
+      </c>
+      <c r="J15" s="25">
+        <v>0</v>
+      </c>
+      <c r="K15" s="26" t="s">
+        <v>66</v>
+      </c>
+      <c r="L15" s="25">
+        <v>0</v>
+      </c>
+      <c r="M15" s="25">
+        <v>0</v>
+      </c>
+      <c r="N15" s="25">
+        <v>0</v>
+      </c>
+      <c r="O15" s="25">
+        <v>0</v>
+      </c>
+      <c r="P15" s="25">
+        <v>0</v>
+      </c>
+      <c r="Q15" s="25">
+        <v>0</v>
+      </c>
+      <c r="R15" s="25">
+        <v>0</v>
+      </c>
+      <c r="S15" s="25">
+        <v>0</v>
+      </c>
+      <c r="T15" s="25">
+        <v>0</v>
+      </c>
+      <c r="U15" s="25">
+        <v>0</v>
+      </c>
+      <c r="V15" s="25">
+        <v>0</v>
+      </c>
+      <c r="W15" s="25">
+        <v>0</v>
+      </c>
+      <c r="X15" s="25">
+        <v>0</v>
+      </c>
+      <c r="Y15" s="25">
+        <v>0</v>
+      </c>
+      <c r="Z15" s="27" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="16" spans="1:26" ht="15">
+      <c r="A16" s="24" t="s">
+        <v>71</v>
+      </c>
+      <c r="B16" s="24" t="s">
+        <v>71</v>
+      </c>
+      <c r="C16" s="24" t="s">
+        <v>71</v>
+      </c>
+      <c r="D16" s="24" t="s">
+        <v>71</v>
+      </c>
+      <c r="E16" s="25">
+        <v>0</v>
+      </c>
+      <c r="F16" s="25">
+        <v>0</v>
+      </c>
+      <c r="G16" s="25">
+        <v>0</v>
+      </c>
+      <c r="H16" s="25">
+        <v>0</v>
+      </c>
+      <c r="I16" s="25">
+        <v>0</v>
+      </c>
+      <c r="J16" s="25">
+        <v>0</v>
+      </c>
+      <c r="K16" s="26" t="s">
+        <v>66</v>
+      </c>
+      <c r="L16" s="25">
+        <v>0</v>
+      </c>
+      <c r="M16" s="25">
+        <v>0</v>
+      </c>
+      <c r="N16" s="25">
+        <v>0</v>
+      </c>
+      <c r="O16" s="25">
+        <v>0</v>
+      </c>
+      <c r="P16" s="25">
+        <v>0</v>
+      </c>
+      <c r="Q16" s="25">
+        <v>0</v>
+      </c>
+      <c r="R16" s="25">
+        <v>0</v>
+      </c>
+      <c r="S16" s="25">
+        <v>0</v>
+      </c>
+      <c r="T16" s="25">
+        <v>0</v>
+      </c>
+      <c r="U16" s="25">
+        <v>0</v>
+      </c>
+      <c r="V16" s="25">
+        <v>0</v>
+      </c>
+      <c r="W16" s="25">
+        <v>0</v>
+      </c>
+      <c r="X16" s="25">
+        <v>0</v>
+      </c>
+      <c r="Y16" s="25">
+        <v>0</v>
+      </c>
+      <c r="Z16" s="27" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="17" spans="1:26" ht="15">
+      <c r="A17" s="24" t="s">
+        <v>72</v>
+      </c>
+      <c r="B17" s="24" t="s">
+        <v>72</v>
+      </c>
+      <c r="C17" s="24" t="s">
+        <v>72</v>
+      </c>
+      <c r="D17" s="24" t="s">
+        <v>72</v>
+      </c>
+      <c r="E17" s="25">
+        <v>308402.52</v>
+      </c>
+      <c r="F17" s="25">
+        <v>0</v>
+      </c>
+      <c r="G17" s="25">
+        <v>0</v>
+      </c>
+      <c r="H17" s="25">
+        <v>308402.52</v>
+      </c>
+      <c r="I17" s="25">
+        <v>0</v>
+      </c>
+      <c r="J17" s="25">
+        <v>308402.52</v>
+      </c>
+      <c r="K17" s="26">
+        <v>1</v>
+      </c>
+      <c r="L17" s="25">
+        <v>0</v>
+      </c>
+      <c r="M17" s="25">
+        <v>0</v>
+      </c>
+      <c r="N17" s="25">
+        <v>0</v>
+      </c>
+      <c r="O17" s="25">
+        <v>0</v>
+      </c>
+      <c r="P17" s="25">
+        <v>0</v>
+      </c>
+      <c r="Q17" s="25">
+        <v>0</v>
+      </c>
+      <c r="R17" s="25">
+        <v>0</v>
+      </c>
+      <c r="S17" s="25">
+        <v>-2675.78</v>
+      </c>
+      <c r="T17" s="25">
+        <v>880580.23</v>
+      </c>
+      <c r="U17" s="25">
+        <v>0</v>
+      </c>
+      <c r="V17" s="25">
+        <v>0</v>
+      </c>
+      <c r="W17" s="25">
+        <v>1186306.97</v>
+      </c>
+      <c r="X17" s="25">
+        <v>-175305.29</v>
+      </c>
+      <c r="Y17" s="25">
+        <v>1011001.68</v>
+      </c>
+      <c r="Z17" s="27">
+        <v>3.85</v>
+      </c>
+    </row>
+    <row r="18" spans="1:26" ht="15">
+      <c r="A18" s="24" t="s">
+        <v>70</v>
+      </c>
+      <c r="B18" s="24" t="s">
+        <v>70</v>
+      </c>
+      <c r="C18" s="24" t="s">
+        <v>70</v>
+      </c>
+      <c r="D18" s="24" t="s">
+        <v>70</v>
+      </c>
+      <c r="E18" s="25">
+        <v>299499.2</v>
+      </c>
+      <c r="F18" s="25">
+        <v>0</v>
+      </c>
+      <c r="G18" s="25">
+        <v>0</v>
+      </c>
+      <c r="H18" s="25">
+        <v>299499.2</v>
+      </c>
+      <c r="I18" s="25">
+        <v>0</v>
+      </c>
+      <c r="J18" s="25">
+        <v>299499.2</v>
+      </c>
+      <c r="K18" s="26">
+        <v>1</v>
+      </c>
+      <c r="L18" s="25">
+        <v>0</v>
+      </c>
+      <c r="M18" s="25">
+        <v>0</v>
+      </c>
+      <c r="N18" s="25">
+        <v>0</v>
+      </c>
+      <c r="O18" s="25">
+        <v>0</v>
+      </c>
+      <c r="P18" s="25">
+        <v>0</v>
+      </c>
+      <c r="Q18" s="25">
+        <v>0</v>
+      </c>
+      <c r="R18" s="25">
+        <v>0</v>
+      </c>
+      <c r="S18" s="25">
+        <v>-2598.52</v>
+      </c>
+      <c r="T18" s="25">
+        <v>855174.37</v>
+      </c>
+      <c r="U18" s="25">
+        <v>0</v>
+      </c>
+      <c r="V18" s="25">
+        <v>0</v>
+      </c>
+      <c r="W18" s="25">
+        <v>1152075.05</v>
+      </c>
+      <c r="X18" s="25">
+        <v>0</v>
+      </c>
+      <c r="Y18" s="25">
+        <v>1152075.05</v>
+      </c>
+      <c r="Z18" s="27">
+        <v>3.85</v>
+      </c>
+    </row>
+    <row r="19" spans="1:26" ht="15">
+      <c r="A19" s="24" t="s">
+        <v>71</v>
+      </c>
+      <c r="B19" s="24" t="s">
+        <v>71</v>
+      </c>
+      <c r="C19" s="24" t="s">
+        <v>71</v>
+      </c>
+      <c r="D19" s="24" t="s">
+        <v>71</v>
+      </c>
+      <c r="E19" s="25">
+        <v>0</v>
+      </c>
+      <c r="F19" s="25">
+        <v>0</v>
+      </c>
+      <c r="G19" s="25">
+        <v>0</v>
+      </c>
+      <c r="H19" s="25">
+        <v>0</v>
+      </c>
+      <c r="I19" s="25">
+        <v>0</v>
+      </c>
+      <c r="J19" s="25">
+        <v>0</v>
+      </c>
+      <c r="K19" s="26" t="s">
+        <v>66</v>
+      </c>
+      <c r="L19" s="25">
+        <v>0</v>
+      </c>
+      <c r="M19" s="25">
+        <v>0</v>
+      </c>
+      <c r="N19" s="25">
+        <v>0</v>
+      </c>
+      <c r="O19" s="25">
+        <v>0</v>
+      </c>
+      <c r="P19" s="25">
+        <v>0</v>
+      </c>
+      <c r="Q19" s="25">
+        <v>0</v>
+      </c>
+      <c r="R19" s="25">
+        <v>0</v>
+      </c>
+      <c r="S19" s="25">
+        <v>0</v>
+      </c>
+      <c r="T19" s="25">
+        <v>0</v>
+      </c>
+      <c r="U19" s="25">
+        <v>0</v>
+      </c>
+      <c r="V19" s="25">
+        <v>0</v>
+      </c>
+      <c r="W19" s="25">
+        <v>0</v>
+      </c>
+      <c r="X19" s="25">
+        <v>-0.01</v>
+      </c>
+      <c r="Y19" s="25">
+        <v>-0.01</v>
+      </c>
+      <c r="Z19" s="27" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="20" spans="1:26" ht="15">
+      <c r="A20" s="24" t="s">
+        <v>72</v>
+      </c>
+      <c r="B20" s="24" t="s">
+        <v>72</v>
+      </c>
+      <c r="C20" s="24" t="s">
+        <v>72</v>
+      </c>
+      <c r="D20" s="24" t="s">
+        <v>72</v>
+      </c>
+      <c r="E20" s="25">
+        <v>250126.38</v>
+      </c>
+      <c r="F20" s="25">
+        <v>0</v>
+      </c>
+      <c r="G20" s="25">
+        <v>0</v>
+      </c>
+      <c r="H20" s="25">
+        <v>250126.38</v>
+      </c>
+      <c r="I20" s="25">
+        <v>0</v>
+      </c>
+      <c r="J20" s="25">
+        <v>250126.38</v>
+      </c>
+      <c r="K20" s="26">
+        <v>1</v>
+      </c>
+      <c r="L20" s="25">
+        <v>0</v>
+      </c>
+      <c r="M20" s="25">
+        <v>0</v>
+      </c>
+      <c r="N20" s="25">
+        <v>0</v>
+      </c>
+      <c r="O20" s="25">
+        <v>0</v>
+      </c>
+      <c r="P20" s="25">
+        <v>0</v>
+      </c>
+      <c r="Q20" s="25">
+        <v>0</v>
+      </c>
+      <c r="R20" s="25">
+        <v>0</v>
+      </c>
+      <c r="S20" s="25">
+        <v>-2170.17</v>
+      </c>
+      <c r="T20" s="25">
+        <v>714202.41</v>
+      </c>
+      <c r="U20" s="25">
+        <v>0</v>
+      </c>
+      <c r="V20" s="25">
+        <v>0</v>
+      </c>
+      <c r="W20" s="25">
+        <v>962158.62</v>
+      </c>
+      <c r="X20" s="25">
+        <v>-138433.98000000001</v>
+      </c>
+      <c r="Y20" s="25">
+        <v>823724.64</v>
+      </c>
+      <c r="Z20" s="27">
+        <v>3.85</v>
+      </c>
+    </row>
+    <row r="21" spans="1:26" ht="15">
+      <c r="A21" s="24" t="s">
+        <v>70</v>
+      </c>
+      <c r="B21" s="24" t="s">
+        <v>70</v>
+      </c>
+      <c r="C21" s="24" t="s">
+        <v>70</v>
+      </c>
+      <c r="D21" s="24" t="s">
+        <v>70</v>
+      </c>
+      <c r="E21" s="25">
+        <v>299499.2</v>
+      </c>
+      <c r="F21" s="25">
+        <v>0</v>
+      </c>
+      <c r="G21" s="25">
+        <v>0</v>
+      </c>
+      <c r="H21" s="25">
+        <v>299499.2</v>
+      </c>
+      <c r="I21" s="25">
+        <v>0</v>
+      </c>
+      <c r="J21" s="25">
+        <v>299499.2</v>
+      </c>
+      <c r="K21" s="26">
+        <v>1</v>
+      </c>
+      <c r="L21" s="25">
+        <v>0</v>
+      </c>
+      <c r="M21" s="25">
+        <v>0</v>
+      </c>
+      <c r="N21" s="25">
+        <v>0</v>
+      </c>
+      <c r="O21" s="25">
+        <v>0</v>
+      </c>
+      <c r="P21" s="25">
+        <v>0</v>
+      </c>
+      <c r="Q21" s="25">
+        <v>0</v>
+      </c>
+      <c r="R21" s="25">
+        <v>0</v>
+      </c>
+      <c r="S21" s="25">
+        <v>-2598.52</v>
+      </c>
+      <c r="T21" s="25">
+        <v>855174.37</v>
+      </c>
+      <c r="U21" s="25">
+        <v>0</v>
+      </c>
+      <c r="V21" s="25">
+        <v>0</v>
+      </c>
+      <c r="W21" s="25">
+        <v>1152075.05</v>
+      </c>
+      <c r="X21" s="25">
+        <v>-167990.71</v>
+      </c>
+      <c r="Y21" s="25">
+        <v>984084.34</v>
+      </c>
+      <c r="Z21" s="27">
+        <v>3.85</v>
+      </c>
+    </row>
+    <row r="22" spans="1:26" ht="15">
+      <c r="A22" s="24" t="s">
+        <v>71</v>
+      </c>
+      <c r="B22" s="24" t="s">
+        <v>71</v>
+      </c>
+      <c r="C22" s="24" t="s">
+        <v>71</v>
+      </c>
+      <c r="D22" s="24" t="s">
+        <v>71</v>
+      </c>
+      <c r="E22" s="25">
+        <v>99552.44</v>
+      </c>
+      <c r="F22" s="25">
+        <v>0</v>
+      </c>
+      <c r="G22" s="25">
+        <v>0</v>
+      </c>
+      <c r="H22" s="25">
+        <v>99552.44</v>
+      </c>
+      <c r="I22" s="25">
+        <v>0</v>
+      </c>
+      <c r="J22" s="25">
+        <v>99552.44</v>
+      </c>
+      <c r="K22" s="26">
+        <v>1</v>
+      </c>
+      <c r="L22" s="25">
+        <v>0</v>
+      </c>
+      <c r="M22" s="25">
+        <v>0</v>
+      </c>
+      <c r="N22" s="25">
+        <v>0</v>
+      </c>
+      <c r="O22" s="25">
+        <v>0</v>
+      </c>
+      <c r="P22" s="25">
+        <v>0</v>
+      </c>
+      <c r="Q22" s="25">
+        <v>0</v>
+      </c>
+      <c r="R22" s="25">
+        <v>0</v>
+      </c>
+      <c r="S22" s="25">
+        <v>-863.74</v>
+      </c>
+      <c r="T22" s="25">
+        <v>284267.52000000002</v>
+      </c>
+      <c r="U22" s="25">
+        <v>0</v>
+      </c>
+      <c r="V22" s="25">
+        <v>0</v>
+      </c>
+      <c r="W22" s="25">
+        <v>382956.22</v>
+      </c>
+      <c r="X22" s="25">
+        <v>-53790.18</v>
+      </c>
+      <c r="Y22" s="25">
+        <v>329166.03999999998</v>
+      </c>
+      <c r="Z22" s="27">
+        <v>3.85</v>
+      </c>
+    </row>
+    <row r="23" spans="1:26" ht="15">
+      <c r="A23" s="24" t="s">
+        <v>72</v>
+      </c>
+      <c r="B23" s="24" t="s">
+        <v>72</v>
+      </c>
+      <c r="C23" s="24" t="s">
+        <v>72</v>
+      </c>
+      <c r="D23" s="24" t="s">
+        <v>72</v>
+      </c>
+      <c r="E23" s="25">
+        <v>250126.38</v>
+      </c>
+      <c r="F23" s="25">
+        <v>0</v>
+      </c>
+      <c r="G23" s="25">
+        <v>0</v>
+      </c>
+      <c r="H23" s="25">
+        <v>250126.38</v>
+      </c>
+      <c r="I23" s="25">
+        <v>0</v>
+      </c>
+      <c r="J23" s="25">
+        <v>250126.38</v>
+      </c>
+      <c r="K23" s="26">
+        <v>1</v>
+      </c>
+      <c r="L23" s="25">
+        <v>0</v>
+      </c>
+      <c r="M23" s="25">
+        <v>0</v>
+      </c>
+      <c r="N23" s="25">
+        <v>0</v>
+      </c>
+      <c r="O23" s="25">
+        <v>0</v>
+      </c>
+      <c r="P23" s="25">
+        <v>0</v>
+      </c>
+      <c r="Q23" s="25">
+        <v>0</v>
+      </c>
+      <c r="R23" s="25">
+        <v>0</v>
+      </c>
+      <c r="S23" s="25">
+        <v>-2170.17</v>
+      </c>
+      <c r="T23" s="25">
+        <v>714202.41</v>
+      </c>
+      <c r="U23" s="25">
+        <v>0</v>
+      </c>
+      <c r="V23" s="25">
+        <v>0</v>
+      </c>
+      <c r="W23" s="25">
+        <v>962158.62</v>
+      </c>
+      <c r="X23" s="25">
+        <v>-138433.98000000001</v>
+      </c>
+      <c r="Y23" s="25">
+        <v>823724.64</v>
+      </c>
+      <c r="Z23" s="27">
+        <v>3.85</v>
+      </c>
+    </row>
+    <row r="24" spans="1:26" ht="15">
+      <c r="A24" s="24" t="s">
+        <v>70</v>
+      </c>
+      <c r="B24" s="24" t="s">
+        <v>70</v>
+      </c>
+      <c r="C24" s="24" t="s">
+        <v>70</v>
+      </c>
+      <c r="D24" s="24" t="s">
+        <v>70</v>
+      </c>
+      <c r="E24" s="25">
+        <v>500252.76</v>
+      </c>
+      <c r="F24" s="25">
+        <v>0</v>
+      </c>
+      <c r="G24" s="25">
+        <v>0</v>
+      </c>
+      <c r="H24" s="25">
+        <v>500252.76</v>
+      </c>
+      <c r="I24" s="25">
+        <v>0</v>
+      </c>
+      <c r="J24" s="25">
+        <v>500252.76</v>
+      </c>
+      <c r="K24" s="26">
+        <v>1</v>
+      </c>
+      <c r="L24" s="25">
+        <v>0</v>
+      </c>
+      <c r="M24" s="25">
+        <v>0</v>
+      </c>
+      <c r="N24" s="25">
+        <v>0</v>
+      </c>
+      <c r="O24" s="25">
+        <v>0</v>
+      </c>
+      <c r="P24" s="25">
+        <v>0</v>
+      </c>
+      <c r="Q24" s="25">
+        <v>0</v>
+      </c>
+      <c r="R24" s="25">
+        <v>0</v>
+      </c>
+      <c r="S24" s="25">
+        <v>-4340.26</v>
+      </c>
+      <c r="T24" s="25">
+        <v>1428354.21</v>
+      </c>
+      <c r="U24" s="25">
+        <v>0</v>
+      </c>
+      <c r="V24" s="25">
+        <v>0</v>
+      </c>
+      <c r="W24" s="25">
+        <v>1924266.71</v>
+      </c>
+      <c r="X24" s="25">
+        <v>-284456.12</v>
+      </c>
+      <c r="Y24" s="25">
+        <v>1639810.59</v>
+      </c>
+      <c r="Z24" s="27">
+        <v>3.85</v>
+      </c>
+    </row>
+    <row r="25" spans="1:26" ht="15">
+      <c r="A25" s="28" t="s">
+        <v>67</v>
+      </c>
+      <c r="B25" s="29" t="s">
+        <v>68</v>
+      </c>
+      <c r="C25" s="29" t="s">
+        <v>68</v>
+      </c>
+      <c r="D25" s="29" t="s">
+        <v>68</v>
+      </c>
+      <c r="E25" s="30">
+        <v>3133341.12</v>
+      </c>
+      <c r="F25" s="30">
+        <v>0</v>
+      </c>
+      <c r="G25" s="30">
+        <v>0</v>
+      </c>
+      <c r="H25" s="30">
+        <v>3133341.12</v>
+      </c>
+      <c r="I25" s="30">
+        <v>0</v>
+      </c>
+      <c r="J25" s="30">
+        <v>3133341.12</v>
+      </c>
+      <c r="K25" s="31" t="s">
+        <v>66</v>
+      </c>
+      <c r="L25" s="30">
+        <v>0</v>
+      </c>
+      <c r="M25" s="30">
+        <v>0</v>
+      </c>
+      <c r="N25" s="30">
+        <v>0</v>
+      </c>
+      <c r="O25" s="30">
+        <v>0</v>
+      </c>
+      <c r="P25" s="30">
+        <v>0</v>
+      </c>
+      <c r="Q25" s="30">
+        <v>0</v>
+      </c>
+      <c r="R25" s="30">
+        <v>0</v>
+      </c>
+      <c r="S25" s="30">
+        <v>-27185.58</v>
+      </c>
+      <c r="T25" s="30">
+        <v>8946683.0299999993</v>
+      </c>
+      <c r="U25" s="30">
+        <v>0</v>
+      </c>
+      <c r="V25" s="30">
+        <v>0</v>
+      </c>
+      <c r="W25" s="30">
+        <v>12052838.57</v>
+      </c>
+      <c r="X25" s="30">
+        <v>-1521263.21</v>
+      </c>
+      <c r="Y25" s="30">
+        <v>10531575.359999999</v>
+      </c>
+      <c r="Z25" s="32" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="26" spans="1:26" ht="13.5" thickBot="1">
+      <c r="A26" s="33" t="s">
+        <v>69</v>
+      </c>
+      <c r="B26" s="34" t="s">
+        <v>68</v>
+      </c>
+      <c r="C26" s="34" t="s">
+        <v>68</v>
+      </c>
+      <c r="D26" s="34" t="s">
+        <v>68</v>
+      </c>
+      <c r="E26" s="35">
+        <v>3133341.12</v>
+      </c>
+      <c r="F26" s="35">
+        <v>0</v>
+      </c>
+      <c r="G26" s="35">
+        <v>0</v>
+      </c>
+      <c r="H26" s="35">
+        <v>3133341.12</v>
+      </c>
+      <c r="I26" s="35">
+        <v>0</v>
+      </c>
+      <c r="J26" s="35">
+        <v>3133341.12</v>
+      </c>
+      <c r="K26" s="36" t="s">
+        <v>66</v>
+      </c>
+      <c r="L26" s="35">
+        <v>0</v>
+      </c>
+      <c r="M26" s="35">
+        <v>0</v>
+      </c>
+      <c r="N26" s="35">
+        <v>0</v>
+      </c>
+      <c r="O26" s="35">
+        <v>0</v>
+      </c>
+      <c r="P26" s="35">
+        <v>0</v>
+      </c>
+      <c r="Q26" s="35">
+        <v>0</v>
+      </c>
+      <c r="R26" s="35">
+        <v>0</v>
+      </c>
+      <c r="S26" s="35">
+        <v>-27185.58</v>
+      </c>
+      <c r="T26" s="35">
+        <v>8946683.0299999993</v>
+      </c>
+      <c r="U26" s="35">
+        <v>0</v>
+      </c>
+      <c r="V26" s="35">
+        <v>0</v>
+      </c>
+      <c r="W26" s="35">
+        <v>12052838.57</v>
+      </c>
+      <c r="X26" s="35">
+        <v>-1521263.21</v>
+      </c>
+      <c r="Y26" s="35">
+        <v>10531575.359999999</v>
+      </c>
+      <c r="Z26" s="37" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="27" spans="1:26" ht="13.5" thickTop="1"/>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>